--- a/output/Glen_Brook/Cash_Reconciliation_Report_Database.xlsx
+++ b/output/Glen_Brook/Cash_Reconciliation_Report_Database.xlsx
@@ -423,10 +423,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GLEN BROOK REHABILITATION OPERATING XXXXXX2944:</v>
+        <v>RFMS Account # ****2318:</v>
       </c>
       <c r="B3" t="str">
-        <v>$2,102,524.37</v>
+        <v>$103,262.60</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -434,10 +434,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GLEN BROOK REHABILITATION PAYROLL XXXXXX3953:</v>
+        <v>Analyzed Checking XXXXXX2969:</v>
       </c>
       <c r="B4" t="str">
-        <v>$1,048,474.73</v>
+        <v>$471,035.82</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -445,10 +445,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GLEN BROOK REHABILITATION XXXXXX2951:</v>
+        <v>GLEN BROOK REHABILITATION PAYROLL XXXXXX3953:</v>
       </c>
       <c r="B5" t="str">
-        <v>$1,631,288.55</v>
+        <v>$1,048,474.73</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -456,10 +456,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GLEN BROOK REHABILITATION XXXXXX2969:</v>
+        <v>GLEN BROOK REHABILITATION XXXXXX2951:</v>
       </c>
       <c r="B6" t="str">
-        <v>$471,035.82</v>
+        <v>$1,631,288.55</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -467,10 +467,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>RFMS Account # ****2318:</v>
+        <v>GLEN BROOK REHABILITATION HEALTHCARE CENTER LLC OPERATING XXXXXX2944:</v>
       </c>
       <c r="B7" t="str">
-        <v>$103,262.60</v>
+        <v>$2,102,524.37</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -536,10 +536,10 @@
         <v>07/23/2025</v>
       </c>
       <c r="B13" t="str">
-        <v>Deposit 07/23/2025</v>
+        <v>ACH 7/23/2025</v>
       </c>
       <c r="C13" t="str">
-        <v>$3,926.62</v>
+        <v>$2,197.95</v>
       </c>
     </row>
     <row r="14">
@@ -547,10 +547,10 @@
         <v>07/23/2025</v>
       </c>
       <c r="B14" t="str">
-        <v>ACH 7/23/2025</v>
+        <v>Apploi 07/23/2025</v>
       </c>
       <c r="C14" t="str">
-        <v>$2,197.95</v>
+        <v>$200.00</v>
       </c>
     </row>
     <row r="15">
@@ -561,7 +561,7 @@
         <v>Deposit 07/23/2025</v>
       </c>
       <c r="C15" t="str">
-        <v>$47,334.98</v>
+        <v>$3,926.62</v>
       </c>
     </row>
     <row r="16">
@@ -569,10 +569,10 @@
         <v>07/23/2025</v>
       </c>
       <c r="B16" t="str">
-        <v>Apploi 07/23/2025</v>
+        <v>Deposit 07/23/2025</v>
       </c>
       <c r="C16" t="str">
-        <v>$200.00</v>
+        <v>$47,334.98</v>
       </c>
     </row>
     <row r="17">
